--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/oct-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/oct-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1802,7 +1802,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>584264-191-CM26</t>
+          <t>584264-190-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1515.35</v>
+        <v>35035.02</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>584264-190-CM26</t>
+          <t>4075-202-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1892,32 +1892,32 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.255.500-7</t>
+          <t>69.150.901-K</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
+          <t>I MUNICIPALIDAD DE YUMBEL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1926,13 +1926,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>35035.02</v>
+        <v>35950.91</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>643-257-CM26</t>
+          <t>584264-191-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1957,27 +1957,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.817.000-4</t>
+          <t>69.255.500-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION V REGION</t>
+          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1527.68</v>
+        <v>1515.35</v>
       </c>
     </row>
     <row r="25">
@@ -2062,7 +2062,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4075-202-CM26</t>
+          <t>643-257-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2087,32 +2087,32 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.150.901-K</t>
+          <t>61.817.000-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUMBEL</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION V REGION</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>35950.91</v>
+        <v>1527.68</v>
       </c>
     </row>
     <row r="27">
@@ -2383,7 +2383,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1344158-26-CM26</t>
+          <t>1596-280-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2408,43 +2408,47 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>60.511.110-6</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE AYSÉN DEL GENERAL CARLOS IBÁÑEZ DE</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>FINNING CHILE S A</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>91.489.000-4</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>101829.9</v>
+        <v>68043.28999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>377-467-CM26</t>
+          <t>1596-281-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2469,27 +2473,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2503,7 +2507,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>813.42</v>
+        <v>882.47</v>
       </c>
     </row>
     <row r="33">
@@ -2574,7 +2578,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1596-281-CM26</t>
+          <t>377-467-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2599,27 +2603,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2633,13 +2637,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>882.47</v>
+        <v>813.42</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1596-280-CM26</t>
+          <t>1344158-26-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2664,47 +2668,43 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>60.511.110-6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE AYSÉN DEL GENERAL CARLOS IBÁÑEZ DE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>FINNING CHILE S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>91.489.000-4</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>68043.28999999999</v>
+        <v>101829.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2369-149-CM26</t>
+          <t>727202-233-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2729,47 +2729,43 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.349.970-7</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>43706.87</v>
+        <v>35756.62</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1079563-449-CM26</t>
+          <t>638-152-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2794,32 +2790,32 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.978.680-7</t>
+          <t>61.824.000-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVIU REGION DE MAGALLANES Y DE LA ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2828,13 +2824,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>34940.12</v>
+        <v>945.77</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4988-116-CM26</t>
+          <t>638-151-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2859,41 +2855,41 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.824.000-2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>SERVIU REGION DE MAGALLANES Y DE LA ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>Biobío</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>EPYSA BUSES LIMITADA</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>77.824.870-0</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>544269.13</v>
+        <v>23927.4</v>
       </c>
     </row>
     <row r="39">
@@ -2964,7 +2960,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>638-151-CM26</t>
+          <t>1079563-449-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2989,32 +2985,32 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.824.000-2</t>
+          <t>61.978.680-7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVIU REGION DE MAGALLANES Y DE LA ANTARTICA CHILENA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3023,13 +3019,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>23927.4</v>
+        <v>34940.12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>638-152-CM26</t>
+          <t>4988-116-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3054,32 +3050,32 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.824.000-2</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVIU REGION DE MAGALLANES Y DE LA ANTARTICA CHILENA</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>EPYSA BUSES LIMITADA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>77.824.870-0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3088,13 +3084,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>945.77</v>
+        <v>544269.13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3453-497-CM26</t>
+          <t>2369-149-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3109,7 +3105,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3119,32 +3115,32 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3153,13 +3149,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2969.49</v>
+        <v>43706.87</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>564162-1094-CM26</t>
+          <t>4473-384-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3174,7 +3170,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3184,27 +3180,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>69.100.200-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>I.MUNICIPALIDAD DE ROMERAL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TATTERSALL AUTOMOTRIZ S.A.</t>
+          <t>AUTOMOTRIZ BALMACEDA LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>83.019.900-4</t>
+          <t>86.341.100-9</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3214,7 +3210,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>46725.3</v>
+        <v>24374.9</v>
       </c>
     </row>
     <row r="44">
@@ -3285,66 +3281,383 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>3453-497-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>61.979.960-7</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>2969.49</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>564162-1094-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>60.911.000-7</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>TATTERSALL AUTOMOTRIZ S.A.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>83.019.900-4</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>46725.3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>5615-602-CM26</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2239-6-LR25</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>oct-2026</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>69.141.700-K</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Ñuble</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>Biobío</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="n">
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
         <v>35388.62</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2345-557-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>69.070.400-5</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>HVCCSA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>76.758.790-2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>45461.19</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2546-1021-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>9231.309999999999</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1191688-102-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>69.255.300-4</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA COMUNA DE EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>260677.52</v>
       </c>
     </row>
   </sheetData>
